--- a/494/layer1_analysis.xlsx
+++ b/494/layer1_analysis.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,231 +413,231 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS80"/>
+  <dimension ref="A1:AS83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Organism</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Function</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Class</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>sequence</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>struct_type</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>index</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>pull_id</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>length</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>MW</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>PI</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>aromaticity</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>instability_index</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>gravy</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>charge_at_7pH</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>aa_A</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>aa_C</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>aa_D</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>aa_E</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>aa_F</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>aa_G</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>aa_H</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>aa_I</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>aa_K</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>aa_L</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>aa_M</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>aa_N</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>aa_P</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>aa_Q</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>aa_R</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>aa_S</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>aa_T</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>aa_V</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>aa_W</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>aa_Y</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>positive_aa_freq</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>negative_aa_freq</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>polar_aa_freq</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>hydrophobic_aa_freq</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>LTA_motif_freq</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>max_basic_run</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>gly_freq</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>pro_freq</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>cys_freq</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>aromatic_freq</t>
         </is>
@@ -12136,7 +12124,11 @@
       <c r="G79" t="n">
         <v>78</v>
       </c>
-      <c r="H79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>JP_d1</t>
+        </is>
+      </c>
       <c r="I79" t="n">
         <v>125</v>
       </c>
@@ -12281,7 +12273,11 @@
       <c r="G80" t="n">
         <v>79</v>
       </c>
-      <c r="H80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>JP_d2</t>
+        </is>
+      </c>
       <c r="I80" t="n">
         <v>61</v>
       </c>
@@ -12392,6 +12388,453 @@
       </c>
       <c r="AS80" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>H7C6X6</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Enterococcus faecalis</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>SalB</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>CAP/SCP</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>MKKRLFASVLLCSLTLSAIATPSIALADNVDKKIEEKNQEISSLKAKQGDLASQVSSLEA EVSSVFDESMALREQKQTLKAKSEQLQQEITNLNQRIEKRNEAIKNQARDVQVNGQSTTM LDAVLDADSVADAISRVQAVSTIVSANNDLMQQQKEDKQAVVDKKAENEKKVKQLEATEA ELETKRQDLLSKQSELNVMKASLALEQSSAESSKAGLEKQKAAAEAEQARLAAEQKAAAE KAKQAAAKPAKAEVKAEAPVASSSTTEAQAPASSSSATESSTQQTTETTTPSTDNSATEN TGSSSSEQPVQPTTPSDNGNNGGQTGGGTVTPTPEPTPAPSADPTINALNVLRQSLGLRP VVWDAGLAASATARAAQVEAGGIPNDHWSRGDEVIAIMWAPGNSVIMAWYNETNMVTASG SGHRDWEINPGITRVGFGYSGSTIVGHSA</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" t="n">
+        <v>80</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>AF-H7C6X6-F1</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>449</v>
+      </c>
+      <c r="J81" t="n">
+        <v>47324.7819</v>
+      </c>
+      <c r="K81" t="n">
+        <v>5.005662345886231</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0.022271714922049</v>
+      </c>
+      <c r="M81" t="n">
+        <v>45.54432071269488</v>
+      </c>
+      <c r="N81" t="n">
+        <v>-0.5456570155902004</v>
+      </c>
+      <c r="O81" t="n">
+        <v>-13.15191799558207</v>
+      </c>
+      <c r="P81" t="n">
+        <v>14.69933184855234</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0.22271714922049</v>
+      </c>
+      <c r="R81" t="n">
+        <v>4.454342984409799</v>
+      </c>
+      <c r="S81" t="n">
+        <v>8.46325167037862</v>
+      </c>
+      <c r="T81" t="n">
+        <v>0.6681514476614699</v>
+      </c>
+      <c r="U81" t="n">
+        <v>5.122494432071269</v>
+      </c>
+      <c r="V81" t="n">
+        <v>0.6681514476614699</v>
+      </c>
+      <c r="W81" t="n">
+        <v>3.786191536748329</v>
+      </c>
+      <c r="X81" t="n">
+        <v>6.904231625835189</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>6.6815144766147</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>1.78173719376392</v>
+      </c>
+      <c r="AA81" t="n">
+        <v>5.122494432071269</v>
+      </c>
+      <c r="AB81" t="n">
+        <v>4.008908685968819</v>
+      </c>
+      <c r="AC81" t="n">
+        <v>7.349665924276169</v>
+      </c>
+      <c r="AD81" t="n">
+        <v>3.11804008908686</v>
+      </c>
+      <c r="AE81" t="n">
+        <v>11.35857461024499</v>
+      </c>
+      <c r="AF81" t="n">
+        <v>7.572383073496659</v>
+      </c>
+      <c r="AG81" t="n">
+        <v>6.458797327394209</v>
+      </c>
+      <c r="AH81" t="n">
+        <v>1.11358574610245</v>
+      </c>
+      <c r="AI81" t="n">
+        <v>0.44543429844098</v>
+      </c>
+      <c r="AJ81" t="n">
+        <v>0.1069042316258352</v>
+      </c>
+      <c r="AK81" t="n">
+        <v>0.1291759465478842</v>
+      </c>
+      <c r="AL81" t="n">
+        <v>0.3140311804008908</v>
+      </c>
+      <c r="AM81" t="n">
+        <v>0.356347438752784</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>0.0155902004454343</v>
+      </c>
+      <c r="AO81" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP81" t="n">
+        <v>0.05122494432071269</v>
+      </c>
+      <c r="AQ81" t="n">
+        <v>0.0400890868596882</v>
+      </c>
+      <c r="AR81" t="n">
+        <v>0.0022271714922049</v>
+      </c>
+      <c r="AS81" t="n">
+        <v>0.022271714922049</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>H7C6X6</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Enterococcus faecalis</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>SalB domain 1 (long)</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>CAP/SCP</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>SIALADNVDKKIEEKNQEISSLKAKQGDLASQVSSLEA EVSSVFDESMALREQKQTLKAKSEQLQQEITNLNQRIEKRNEAIKNQARDVQVNGQSTTM LDAVLDADSVADAISRVQAVSTIVSANNDLMQQQKEDKQAVVDKKAENEKKVKQLEATEA ELETKRQDLLSKQSELNVMKASLALEQSSAESSKAGLEKQKAAAEAEQARLAAEQKAAAE KAKQAAAKPA</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" t="n">
+        <v>81</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Sal_d1</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>228</v>
+      </c>
+      <c r="J82" t="n">
+        <v>24803.4189</v>
+      </c>
+      <c r="K82" t="n">
+        <v>5.178339195251463</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0.004385964912280702</v>
+      </c>
+      <c r="M82" t="n">
+        <v>49.98859649122808</v>
+      </c>
+      <c r="N82" t="n">
+        <v>-0.7491228070175439</v>
+      </c>
+      <c r="O82" t="n">
+        <v>-5.479254663533986</v>
+      </c>
+      <c r="P82" t="n">
+        <v>16.66666666666667</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" t="n">
+        <v>5.701754385964913</v>
+      </c>
+      <c r="S82" t="n">
+        <v>11.40350877192983</v>
+      </c>
+      <c r="T82" t="n">
+        <v>0.4385964912280702</v>
+      </c>
+      <c r="U82" t="n">
+        <v>1.315789473684211</v>
+      </c>
+      <c r="V82" t="n">
+        <v>0</v>
+      </c>
+      <c r="W82" t="n">
+        <v>3.508771929824561</v>
+      </c>
+      <c r="X82" t="n">
+        <v>11.8421052631579</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>8.771929824561404</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>1.754385964912281</v>
+      </c>
+      <c r="AA82" t="n">
+        <v>4.824561403508772</v>
+      </c>
+      <c r="AB82" t="n">
+        <v>0.4385964912280702</v>
+      </c>
+      <c r="AC82" t="n">
+        <v>10.96491228070176</v>
+      </c>
+      <c r="AD82" t="n">
+        <v>3.070175438596491</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>9.649122807017545</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>3.070175438596491</v>
+      </c>
+      <c r="AG82" t="n">
+        <v>6.578947368421052</v>
+      </c>
+      <c r="AH82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ82" t="n">
+        <v>0.1491228070175439</v>
+      </c>
+      <c r="AK82" t="n">
+        <v>0.1710526315789474</v>
+      </c>
+      <c r="AL82" t="n">
+        <v>0.2850877192982456</v>
+      </c>
+      <c r="AM82" t="n">
+        <v>0.3771929824561404</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>0.02192982456140351</v>
+      </c>
+      <c r="AO82" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP82" t="n">
+        <v>0.0131578947368421</v>
+      </c>
+      <c r="AQ82" t="n">
+        <v>0.004385964912280702</v>
+      </c>
+      <c r="AR82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS82" t="n">
+        <v>0.004385964912280702</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>H7C6X6</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Enterococcus faecalis</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>SalB domain 2 (globular)</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>CAP/SCP</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>ADPTINALNVLRQSLGLRP VVWDAGLAASATARAAQVEAGGIPNDHWSRGDEVIAIMWAPGNSVIMAWYNETNMVTASG SGHRDWEINPGITRVGFGYSGSTIVGHSA</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" t="n">
+        <v>82</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Sal_d2</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>108</v>
+      </c>
+      <c r="J83" t="n">
+        <v>11358.533</v>
+      </c>
+      <c r="K83" t="n">
+        <v>5.400011253356933</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0.07407407407407407</v>
+      </c>
+      <c r="M83" t="n">
+        <v>18.38518518518518</v>
+      </c>
+      <c r="N83" t="n">
+        <v>-0.02777777777777779</v>
+      </c>
+      <c r="O83" t="n">
+        <v>-2.927815196188098</v>
+      </c>
+      <c r="P83" t="n">
+        <v>13.88888888888889</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" t="n">
+        <v>4.62962962962963</v>
+      </c>
+      <c r="S83" t="n">
+        <v>3.703703703703704</v>
+      </c>
+      <c r="T83" t="n">
+        <v>0.9259259259259259</v>
+      </c>
+      <c r="U83" t="n">
+        <v>12.03703703703704</v>
+      </c>
+      <c r="V83" t="n">
+        <v>2.777777777777778</v>
+      </c>
+      <c r="W83" t="n">
+        <v>7.407407407407407</v>
+      </c>
+      <c r="X83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>4.62962962962963</v>
+      </c>
+      <c r="Z83" t="n">
+        <v>2.777777777777778</v>
+      </c>
+      <c r="AA83" t="n">
+        <v>6.481481481481482</v>
+      </c>
+      <c r="AB83" t="n">
+        <v>4.62962962962963</v>
+      </c>
+      <c r="AC83" t="n">
+        <v>1.851851851851852</v>
+      </c>
+      <c r="AD83" t="n">
+        <v>5.555555555555555</v>
+      </c>
+      <c r="AE83" t="n">
+        <v>8.333333333333334</v>
+      </c>
+      <c r="AF83" t="n">
+        <v>5.555555555555555</v>
+      </c>
+      <c r="AG83" t="n">
+        <v>8.333333333333334</v>
+      </c>
+      <c r="AH83" t="n">
+        <v>4.62962962962963</v>
+      </c>
+      <c r="AI83" t="n">
+        <v>1.851851851851852</v>
+      </c>
+      <c r="AJ83" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="AK83" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="AL83" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="AM83" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO83" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP83" t="n">
+        <v>0.1203703703703704</v>
+      </c>
+      <c r="AQ83" t="n">
+        <v>0.04629629629629629</v>
+      </c>
+      <c r="AR83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS83" t="n">
+        <v>0.07407407407407407</v>
       </c>
     </row>
   </sheetData>
